--- a/Descuentos/Productos.xlsx
+++ b/Descuentos/Productos.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Stock" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stock" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -681,7 +681,7 @@
         </is>
       </c>
       <c r="C24" s="2" t="n">
-        <v>-24</v>
+        <v>-72</v>
       </c>
     </row>
     <row r="25">
@@ -694,7 +694,7 @@
         </is>
       </c>
       <c r="C25" s="2" t="n">
-        <v>-24</v>
+        <v>-72</v>
       </c>
     </row>
     <row r="26">
@@ -740,7 +740,7 @@
         </is>
       </c>
       <c r="C29" s="2" t="n">
-        <v>-12</v>
+        <v>-36</v>
       </c>
     </row>
     <row r="30">
@@ -830,7 +830,7 @@
         </is>
       </c>
       <c r="C37" s="2" t="n">
-        <v>-2</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="38">
@@ -898,7 +898,7 @@
         </is>
       </c>
       <c r="C43" s="2" t="n">
-        <v>-2</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="44">
@@ -1439,7 +1439,7 @@
         </is>
       </c>
       <c r="C92" s="2" t="n">
-        <v>-72</v>
+        <v>-216</v>
       </c>
     </row>
     <row r="93">
@@ -2013,7 +2013,7 @@
         </is>
       </c>
       <c r="C144" s="2" t="n">
-        <v>-28</v>
+        <v>-84</v>
       </c>
     </row>
     <row r="145">
@@ -2257,7 +2257,7 @@
         </is>
       </c>
       <c r="C166" s="2" t="n">
-        <v>-24</v>
+        <v>-72</v>
       </c>
     </row>
     <row r="167">
@@ -2380,7 +2380,7 @@
         </is>
       </c>
       <c r="C177" s="2" t="n">
-        <v>-20</v>
+        <v>-60</v>
       </c>
     </row>
     <row r="178">
@@ -2470,7 +2470,7 @@
         </is>
       </c>
       <c r="C185" s="2" t="n">
-        <v>-20</v>
+        <v>-60</v>
       </c>
     </row>
     <row r="186">
@@ -2560,7 +2560,7 @@
         </is>
       </c>
       <c r="C193" s="2" t="n">
-        <v>-40</v>
+        <v>-120</v>
       </c>
     </row>
     <row r="194">
@@ -2661,7 +2661,7 @@
         </is>
       </c>
       <c r="C202" s="2" t="n">
-        <v>-40</v>
+        <v>-120</v>
       </c>
     </row>
     <row r="203">
@@ -3026,7 +3026,7 @@
         </is>
       </c>
       <c r="C235" s="2" t="n">
-        <v>-2</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="236">
@@ -3039,7 +3039,7 @@
         </is>
       </c>
       <c r="C236" s="2" t="n">
-        <v>-14</v>
+        <v>-42</v>
       </c>
     </row>
     <row r="237">

--- a/Descuentos/Productos.xlsx
+++ b/Descuentos/Productos.xlsx
@@ -889,13 +889,13 @@
         </is>
       </c>
       <c r="D5" s="42" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E5" s="42" t="n">
         <v>-2</v>
       </c>
       <c r="F5" s="43" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="G5" s="38" t="n"/>
       <c r="H5" s="38" t="n"/>
@@ -925,13 +925,13 @@
         </is>
       </c>
       <c r="D6" s="42" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E6" s="42" t="n">
         <v>-1</v>
       </c>
       <c r="F6" s="43" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G6" s="38" t="n"/>
       <c r="H6" s="38" t="n"/>
@@ -1081,13 +1081,13 @@
         </is>
       </c>
       <c r="D11" s="42" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E11" s="42" t="n">
         <v>-1</v>
       </c>
       <c r="F11" s="43" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G11" s="38" t="n"/>
       <c r="H11" s="38" t="n"/>
@@ -1233,13 +1233,13 @@
         </is>
       </c>
       <c r="D16" s="42" t="n">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E16" s="42" t="n">
         <v>-1</v>
       </c>
       <c r="F16" s="43" t="n">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="G16" s="38" t="n"/>
       <c r="H16" s="38" t="n"/>
@@ -1269,13 +1269,13 @@
         </is>
       </c>
       <c r="D17" s="42" t="n">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E17" s="42" t="n">
         <v>-1</v>
       </c>
       <c r="F17" s="43" t="n">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="G17" s="38" t="n"/>
       <c r="H17" s="38" t="n"/>
@@ -1305,13 +1305,13 @@
         </is>
       </c>
       <c r="D18" s="42" t="n">
-        <v>260</v>
+        <v>252</v>
       </c>
       <c r="E18" s="42" t="n">
         <v>-8</v>
       </c>
       <c r="F18" s="43" t="n">
-        <v>252</v>
+        <v>244</v>
       </c>
       <c r="G18" s="38" t="n"/>
       <c r="H18" s="38" t="n"/>
@@ -1341,13 +1341,13 @@
         </is>
       </c>
       <c r="D19" s="42" t="n">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E19" s="42" t="n">
         <v>-1</v>
       </c>
       <c r="F19" s="43" t="n">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="G19" s="38" t="n"/>
       <c r="H19" s="38" t="n"/>
@@ -1441,13 +1441,13 @@
         </is>
       </c>
       <c r="D22" s="42" t="n">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E22" s="42" t="n">
         <v>-1</v>
       </c>
       <c r="F22" s="43" t="n">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G22" s="38" t="n"/>
       <c r="H22" s="38" t="n"/>
@@ -1589,13 +1589,13 @@
         </is>
       </c>
       <c r="D27" s="42" t="n">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="E27" s="42" t="n">
         <v>-2</v>
       </c>
       <c r="F27" s="43" t="n">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="G27" s="38" t="n"/>
       <c r="H27" s="38" t="n"/>
@@ -1753,13 +1753,13 @@
         </is>
       </c>
       <c r="D32" s="42" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E32" s="42" t="n">
         <v>-2</v>
       </c>
       <c r="F32" s="43" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="G32" s="38" t="n"/>
       <c r="H32" s="38" t="n"/>
@@ -1789,13 +1789,13 @@
         </is>
       </c>
       <c r="D33" s="42" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E33" s="42" t="n">
         <v>-3</v>
       </c>
       <c r="F33" s="43" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="G33" s="38" t="n"/>
       <c r="H33" s="38" t="n"/>
@@ -1825,13 +1825,13 @@
         </is>
       </c>
       <c r="D34" s="42" t="n">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E34" s="42" t="n">
         <v>-1</v>
       </c>
       <c r="F34" s="43" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G34" s="38" t="n"/>
       <c r="H34" s="38" t="n"/>
@@ -1893,13 +1893,13 @@
         </is>
       </c>
       <c r="D36" s="42" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E36" s="42" t="n">
         <v>-1</v>
       </c>
       <c r="F36" s="43" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G36" s="38" t="n"/>
       <c r="H36" s="38" t="n"/>
@@ -1929,13 +1929,13 @@
         </is>
       </c>
       <c r="D37" s="42" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E37" s="42" t="n">
         <v>-1</v>
       </c>
       <c r="F37" s="43" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G37" s="38" t="n"/>
       <c r="H37" s="38" t="n"/>
@@ -2061,13 +2061,13 @@
         </is>
       </c>
       <c r="D41" s="42" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E41" s="42" t="n">
         <v>-1</v>
       </c>
       <c r="F41" s="43" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G41" s="38" t="n"/>
       <c r="H41" s="38" t="n"/>
@@ -2097,13 +2097,13 @@
         </is>
       </c>
       <c r="D42" s="42" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="E42" s="42" t="n">
         <v>-1</v>
       </c>
       <c r="F42" s="43" t="n">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="G42" s="38" t="n"/>
       <c r="H42" s="38" t="n"/>
@@ -2161,13 +2161,13 @@
         </is>
       </c>
       <c r="D44" s="42" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E44" s="42" t="n">
         <v>-1</v>
       </c>
       <c r="F44" s="43" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G44" s="38" t="n"/>
       <c r="H44" s="38" t="n"/>
@@ -2197,13 +2197,13 @@
         </is>
       </c>
       <c r="D45" s="42" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E45" s="42" t="n">
         <v>-1</v>
       </c>
       <c r="F45" s="43" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G45" s="38" t="n"/>
       <c r="H45" s="38" t="n"/>
@@ -2233,13 +2233,13 @@
         </is>
       </c>
       <c r="D46" s="42" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E46" s="42" t="n">
         <v>-1</v>
       </c>
       <c r="F46" s="43" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G46" s="38" t="n"/>
       <c r="H46" s="38" t="n"/>
@@ -2301,13 +2301,13 @@
         </is>
       </c>
       <c r="D48" s="42" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E48" s="42" t="n">
         <v>-2</v>
       </c>
       <c r="F48" s="43" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="G48" s="38" t="n"/>
       <c r="H48" s="38" t="n"/>
@@ -2337,13 +2337,13 @@
         </is>
       </c>
       <c r="D49" s="42" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E49" s="42" t="n">
         <v>-1</v>
       </c>
       <c r="F49" s="43" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G49" s="38" t="n"/>
       <c r="H49" s="38" t="n"/>
@@ -2437,13 +2437,13 @@
         </is>
       </c>
       <c r="D52" s="42" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E52" s="42" t="n">
         <v>-1</v>
       </c>
       <c r="F52" s="43" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G52" s="38" t="n"/>
       <c r="H52" s="38" t="n"/>
@@ -2537,13 +2537,13 @@
         </is>
       </c>
       <c r="D55" s="42" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E55" s="42" t="n">
         <v>-2</v>
       </c>
       <c r="F55" s="43" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="G55" s="38" t="n"/>
       <c r="H55" s="38" t="n"/>
@@ -2573,13 +2573,13 @@
         </is>
       </c>
       <c r="D56" s="42" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E56" s="42" t="n">
         <v>-1</v>
       </c>
       <c r="F56" s="43" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G56" s="38" t="n"/>
       <c r="H56" s="38" t="n"/>
@@ -2609,13 +2609,13 @@
         </is>
       </c>
       <c r="D57" s="42" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E57" s="42" t="n">
         <v>-2</v>
       </c>
       <c r="F57" s="43" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G57" s="38" t="n"/>
       <c r="H57" s="38" t="n"/>
@@ -2677,13 +2677,13 @@
         </is>
       </c>
       <c r="D59" s="42" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E59" s="42" t="n">
         <v>-1</v>
       </c>
       <c r="F59" s="43" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G59" s="38" t="n"/>
       <c r="H59" s="38" t="n"/>
@@ -2745,13 +2745,13 @@
         </is>
       </c>
       <c r="D61" s="42" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E61" s="42" t="n">
         <v>-1</v>
       </c>
       <c r="F61" s="43" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G61" s="38" t="n"/>
       <c r="H61" s="38" t="n"/>
@@ -2909,13 +2909,13 @@
         </is>
       </c>
       <c r="D66" s="42" t="n">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="E66" s="42" t="n">
         <v>-3</v>
       </c>
       <c r="F66" s="43" t="n">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="G66" s="38" t="n"/>
       <c r="H66" s="38" t="n"/>
@@ -2945,13 +2945,13 @@
         </is>
       </c>
       <c r="D67" s="42" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E67" s="42" t="n">
         <v>-1</v>
       </c>
       <c r="F67" s="43" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G67" s="38" t="n"/>
       <c r="H67" s="38" t="n"/>
@@ -3045,13 +3045,13 @@
         </is>
       </c>
       <c r="D70" s="42" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E70" s="42" t="n">
         <v>-1</v>
       </c>
       <c r="F70" s="43" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G70" s="38" t="n"/>
       <c r="H70" s="38" t="n"/>
@@ -4157,13 +4157,13 @@
         </is>
       </c>
       <c r="D105" s="42" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="E105" s="42" t="n">
         <v>-12</v>
       </c>
       <c r="F105" s="43" t="n">
-        <v>0</v>
+        <v>-12</v>
       </c>
       <c r="G105" s="38" t="n"/>
       <c r="H105" s="38" t="n"/>
@@ -4225,13 +4225,13 @@
         </is>
       </c>
       <c r="D107" s="42" t="n">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="E107" s="42" t="n">
         <v>-12</v>
       </c>
       <c r="F107" s="43" t="n">
-        <v>7</v>
+        <v>-5</v>
       </c>
       <c r="G107" s="38" t="n"/>
       <c r="H107" s="38" t="n"/>
@@ -4261,13 +4261,13 @@
         </is>
       </c>
       <c r="D108" s="42" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E108" s="42" t="n">
         <v>-2</v>
       </c>
       <c r="F108" s="43" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G108" s="38" t="n"/>
       <c r="H108" s="38" t="n"/>
@@ -4519,13 +4519,13 @@
         </is>
       </c>
       <c r="D116" s="42" t="n">
-        <v>-47</v>
+        <v>-83</v>
       </c>
       <c r="E116" s="42" t="n">
         <v>-36</v>
       </c>
       <c r="F116" s="43" t="n">
-        <v>-83</v>
+        <v>-119</v>
       </c>
       <c r="G116" s="38" t="n"/>
       <c r="H116" s="38" t="n"/>
@@ -4555,13 +4555,13 @@
         </is>
       </c>
       <c r="D117" s="42" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E117" s="42" t="n">
         <v>-1</v>
       </c>
       <c r="F117" s="43" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G117" s="38" t="n"/>
       <c r="H117" s="38" t="n"/>
@@ -4655,13 +4655,13 @@
         </is>
       </c>
       <c r="D120" s="42" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E120" s="42" t="n">
         <v>-1</v>
       </c>
       <c r="F120" s="43" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G120" s="38" t="n"/>
       <c r="H120" s="38" t="n"/>
@@ -4819,13 +4819,13 @@
         </is>
       </c>
       <c r="D125" s="42" t="n">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E125" s="42" t="n">
         <v>-1</v>
       </c>
       <c r="F125" s="43" t="n">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="G125" s="38" t="n"/>
       <c r="H125" s="38" t="n"/>
@@ -5269,13 +5269,13 @@
         </is>
       </c>
       <c r="D139" s="42" t="n">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E139" s="42" t="n">
         <v>-2</v>
       </c>
       <c r="F139" s="43" t="n">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="G139" s="38" t="n"/>
       <c r="H139" s="38" t="n"/>
@@ -5431,13 +5431,13 @@
         </is>
       </c>
       <c r="D144" s="42" t="n">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="E144" s="42" t="n">
         <v>-2</v>
       </c>
       <c r="F144" s="43" t="n">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="G144" s="38" t="n"/>
       <c r="H144" s="38" t="n"/>
@@ -5849,13 +5849,13 @@
         </is>
       </c>
       <c r="D157" s="42" t="n">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="E157" s="42" t="n">
         <v>-2</v>
       </c>
       <c r="F157" s="43" t="n">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="G157" s="38" t="n"/>
       <c r="H157" s="38" t="n"/>
@@ -6039,13 +6039,13 @@
         </is>
       </c>
       <c r="D163" s="42" t="n">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="E163" s="42" t="n">
         <v>-2</v>
       </c>
       <c r="F163" s="43" t="n">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="G163" s="38" t="n"/>
       <c r="H163" s="38" t="n"/>
@@ -6139,13 +6139,13 @@
         </is>
       </c>
       <c r="D166" s="42" t="n">
-        <v>131</v>
+        <v>119</v>
       </c>
       <c r="E166" s="42" t="n">
         <v>-12</v>
       </c>
       <c r="F166" s="43" t="n">
-        <v>119</v>
+        <v>107</v>
       </c>
       <c r="G166" s="38" t="n"/>
       <c r="H166" s="38" t="n"/>
@@ -6175,13 +6175,13 @@
         </is>
       </c>
       <c r="D167" s="42" t="n">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="E167" s="42" t="n">
         <v>-3</v>
       </c>
       <c r="F167" s="43" t="n">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="G167" s="38" t="n"/>
       <c r="H167" s="38" t="n"/>
@@ -6399,13 +6399,13 @@
         </is>
       </c>
       <c r="D174" s="42" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="E174" s="42" t="n">
         <v>-2</v>
       </c>
       <c r="F174" s="43" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G174" s="38" t="n"/>
       <c r="H174" s="38" t="n"/>
@@ -6467,13 +6467,13 @@
         </is>
       </c>
       <c r="D176" s="42" t="n">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="E176" s="42" t="n">
         <v>-4</v>
       </c>
       <c r="F176" s="43" t="n">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="G176" s="38" t="n"/>
       <c r="H176" s="38" t="n"/>
@@ -6567,13 +6567,13 @@
         </is>
       </c>
       <c r="D179" s="42" t="n">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="E179" s="42" t="n">
         <v>-11</v>
       </c>
       <c r="F179" s="43" t="n">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="G179" s="38" t="n"/>
       <c r="H179" s="38" t="n"/>
@@ -6635,13 +6635,13 @@
         </is>
       </c>
       <c r="D181" s="42" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E181" s="42" t="n">
         <v>-1</v>
       </c>
       <c r="F181" s="43" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G181" s="38" t="n"/>
       <c r="H181" s="38" t="n"/>
@@ -6671,13 +6671,13 @@
         </is>
       </c>
       <c r="D182" s="42" t="n">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E182" s="42" t="n">
         <v>-1</v>
       </c>
       <c r="F182" s="43" t="n">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="G182" s="38" t="n"/>
       <c r="H182" s="38" t="n"/>
@@ -6739,13 +6739,13 @@
         </is>
       </c>
       <c r="D184" s="42" t="n">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E184" s="42" t="n">
         <v>-1</v>
       </c>
       <c r="F184" s="43" t="n">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="G184" s="38" t="n"/>
       <c r="H184" s="38" t="n"/>
@@ -6839,13 +6839,13 @@
         </is>
       </c>
       <c r="D187" s="42" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="E187" s="42" t="n">
         <v>-15</v>
       </c>
       <c r="F187" s="43" t="n">
-        <v>1</v>
+        <v>-14</v>
       </c>
       <c r="G187" s="38" t="n"/>
       <c r="H187" s="38" t="n"/>
@@ -6939,13 +6939,13 @@
         </is>
       </c>
       <c r="D190" s="42" t="n">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E190" s="42" t="n">
         <v>-1</v>
       </c>
       <c r="F190" s="43" t="n">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="G190" s="38" t="n"/>
       <c r="H190" s="38" t="n"/>
@@ -6975,13 +6975,13 @@
         </is>
       </c>
       <c r="D191" s="42" t="n">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="E191" s="42" t="n">
         <v>-3</v>
       </c>
       <c r="F191" s="43" t="n">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="G191" s="38" t="n"/>
       <c r="H191" s="38" t="n"/>
@@ -7043,13 +7043,13 @@
         </is>
       </c>
       <c r="D193" s="42" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E193" s="42" t="n">
         <v>-1</v>
       </c>
       <c r="F193" s="43" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G193" s="38" t="n"/>
       <c r="H193" s="38" t="n"/>
@@ -7171,13 +7171,13 @@
         </is>
       </c>
       <c r="D197" s="42" t="n">
-        <v>112</v>
+        <v>101</v>
       </c>
       <c r="E197" s="42" t="n">
         <v>-11</v>
       </c>
       <c r="F197" s="43" t="n">
-        <v>101</v>
+        <v>90</v>
       </c>
       <c r="G197" s="38" t="n"/>
       <c r="H197" s="38" t="n"/>
@@ -7207,13 +7207,13 @@
         </is>
       </c>
       <c r="D198" s="42" t="n">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E198" s="42" t="n">
         <v>-1</v>
       </c>
       <c r="F198" s="43" t="n">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="G198" s="38" t="n"/>
       <c r="H198" s="38" t="n"/>
@@ -7491,13 +7491,13 @@
         </is>
       </c>
       <c r="D207" s="42" t="n">
-        <v>63</v>
+        <v>43</v>
       </c>
       <c r="E207" s="42" t="n">
         <v>-20</v>
       </c>
       <c r="F207" s="43" t="n">
-        <v>43</v>
+        <v>23</v>
       </c>
       <c r="G207" s="38" t="n"/>
       <c r="H207" s="38" t="n"/>
@@ -7655,13 +7655,13 @@
         </is>
       </c>
       <c r="D212" s="42" t="n">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E212" s="42" t="n">
         <v>-1</v>
       </c>
       <c r="F212" s="43" t="n">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="G212" s="38" t="n"/>
       <c r="H212" s="38" t="n"/>
@@ -7691,13 +7691,13 @@
         </is>
       </c>
       <c r="D213" s="42" t="n">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E213" s="42" t="n">
         <v>-2</v>
       </c>
       <c r="F213" s="43" t="n">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="G213" s="38" t="n"/>
       <c r="H213" s="38" t="n"/>
@@ -7727,13 +7727,13 @@
         </is>
       </c>
       <c r="D214" s="42" t="n">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="E214" s="42" t="n">
         <v>-1</v>
       </c>
       <c r="F214" s="43" t="n">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="G214" s="38" t="n"/>
       <c r="H214" s="38" t="n"/>
@@ -7763,13 +7763,13 @@
         </is>
       </c>
       <c r="D215" s="42" t="n">
-        <v>51</v>
+        <v>31</v>
       </c>
       <c r="E215" s="42" t="n">
         <v>-20</v>
       </c>
       <c r="F215" s="43" t="n">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="G215" s="38" t="n"/>
       <c r="H215" s="38" t="n"/>
@@ -7831,13 +7831,13 @@
         </is>
       </c>
       <c r="D217" s="42" t="n">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E217" s="42" t="n">
         <v>-1</v>
       </c>
       <c r="F217" s="43" t="n">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="G217" s="38" t="n"/>
       <c r="H217" s="38" t="n"/>
@@ -7867,13 +7867,13 @@
         </is>
       </c>
       <c r="D218" s="42" t="n">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="E218" s="42" t="n">
         <v>-3</v>
       </c>
       <c r="F218" s="43" t="n">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="G218" s="38" t="n"/>
       <c r="H218" s="38" t="n"/>
@@ -7935,13 +7935,13 @@
         </is>
       </c>
       <c r="D220" s="42" t="n">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E220" s="42" t="n">
         <v>-2</v>
       </c>
       <c r="F220" s="43" t="n">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="G220" s="38" t="n"/>
       <c r="H220" s="38" t="n"/>
@@ -8099,13 +8099,13 @@
         </is>
       </c>
       <c r="D225" s="42" t="n">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="E225" s="42" t="n">
         <v>-2</v>
       </c>
       <c r="F225" s="43" t="n">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="G225" s="38" t="n"/>
       <c r="H225" s="38" t="n"/>
@@ -8263,13 +8263,13 @@
         </is>
       </c>
       <c r="D230" s="42" t="n">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="E230" s="42" t="n">
         <v>-2</v>
       </c>
       <c r="F230" s="43" t="n">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="G230" s="38" t="n"/>
       <c r="H230" s="38" t="n"/>
@@ -8427,13 +8427,13 @@
         </is>
       </c>
       <c r="D235" s="42" t="n">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E235" s="42" t="n">
         <v>-1</v>
       </c>
       <c r="F235" s="43" t="n">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="G235" s="38" t="n"/>
       <c r="H235" s="38" t="n"/>
@@ -8591,13 +8591,13 @@
         </is>
       </c>
       <c r="D240" s="42" t="n">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="E240" s="42" t="n">
         <v>-8</v>
       </c>
       <c r="F240" s="43" t="n">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="G240" s="38" t="n"/>
       <c r="H240" s="38" t="n"/>
@@ -8659,13 +8659,13 @@
         </is>
       </c>
       <c r="D242" s="42" t="n">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E242" s="42" t="n">
         <v>-1</v>
       </c>
       <c r="F242" s="43" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G242" s="38" t="n"/>
       <c r="H242" s="38" t="n"/>
@@ -8759,13 +8759,13 @@
         </is>
       </c>
       <c r="D245" s="42" t="n">
-        <v>854</v>
+        <v>848</v>
       </c>
       <c r="E245" s="42" t="n">
         <v>-6</v>
       </c>
       <c r="F245" s="43" t="n">
-        <v>848</v>
+        <v>842</v>
       </c>
       <c r="G245" s="38" t="n"/>
       <c r="H245" s="38" t="n"/>
@@ -8795,13 +8795,13 @@
         </is>
       </c>
       <c r="D246" s="42" t="n">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="E246" s="42" t="n">
         <v>-2</v>
       </c>
       <c r="F246" s="43" t="n">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="G246" s="38" t="n"/>
       <c r="H246" s="38" t="n"/>
@@ -9051,13 +9051,13 @@
         </is>
       </c>
       <c r="D254" s="42" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E254" s="42" t="n">
         <v>-1</v>
       </c>
       <c r="F254" s="43" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G254" s="38" t="n"/>
       <c r="H254" s="38" t="n"/>
@@ -9245,13 +9245,13 @@
         </is>
       </c>
       <c r="D260" s="42" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E260" s="42" t="n">
         <v>-2</v>
       </c>
       <c r="F260" s="43" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="G260" s="38" t="n"/>
       <c r="H260" s="38" t="n"/>
@@ -9343,13 +9343,13 @@
         </is>
       </c>
       <c r="D263" s="42" t="n">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="E263" s="42" t="n">
         <v>-8</v>
       </c>
       <c r="F263" s="43" t="n">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="G263" s="38" t="n"/>
       <c r="H263" s="38" t="n"/>
@@ -9443,13 +9443,13 @@
         </is>
       </c>
       <c r="D266" s="42" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E266" s="42" t="n">
         <v>-1</v>
       </c>
       <c r="F266" s="43" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G266" s="38" t="n"/>
       <c r="H266" s="38" t="n"/>
@@ -10393,13 +10393,13 @@
         </is>
       </c>
       <c r="D296" s="45" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E296" s="45" t="n">
         <v>-2</v>
       </c>
       <c r="F296" s="43" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="G296" s="38" t="n"/>
       <c r="H296" s="38" t="n"/>
@@ -10439,13 +10439,13 @@
         </is>
       </c>
       <c r="D297" s="45" t="n">
-        <v>896</v>
+        <v>894</v>
       </c>
       <c r="E297" s="45" t="n">
         <v>-2</v>
       </c>
       <c r="F297" s="43" t="n">
-        <v>894</v>
+        <v>892</v>
       </c>
       <c r="G297" s="38" t="n"/>
       <c r="H297" s="38" t="n"/>
@@ -10507,13 +10507,13 @@
         </is>
       </c>
       <c r="D299" s="45" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="E299" s="45" t="n">
         <v>-2</v>
       </c>
       <c r="F299" s="43" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="G299" s="38" t="n"/>
       <c r="H299" s="38" t="n"/>
@@ -10923,13 +10923,13 @@
         </is>
       </c>
       <c r="D311" s="45" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E311" s="45" t="n">
         <v>-2</v>
       </c>
       <c r="F311" s="43" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G311" s="38" t="n"/>
       <c r="H311" s="38" t="n"/>
@@ -10959,13 +10959,13 @@
         </is>
       </c>
       <c r="D312" s="45" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E312" s="45" t="n">
         <v>-2</v>
       </c>
       <c r="F312" s="43" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G312" s="38" t="n"/>
       <c r="H312" s="38" t="n"/>
@@ -11713,13 +11713,13 @@
         </is>
       </c>
       <c r="D337" s="45" t="n">
-        <v>-6</v>
+        <v>-9</v>
       </c>
       <c r="E337" s="45" t="n">
         <v>-3</v>
       </c>
       <c r="F337" s="43" t="n">
-        <v>-9</v>
+        <v>-12</v>
       </c>
       <c r="G337" s="38" t="n"/>
       <c r="H337" s="38" t="n"/>
@@ -11989,13 +11989,13 @@
         </is>
       </c>
       <c r="D346" s="45" t="n">
-        <v>-6</v>
+        <v>-9</v>
       </c>
       <c r="E346" s="45" t="n">
         <v>-3</v>
       </c>
       <c r="F346" s="43" t="n">
-        <v>-9</v>
+        <v>-12</v>
       </c>
       <c r="G346" s="38" t="n"/>
       <c r="H346" s="38" t="n"/>
@@ -12085,13 +12085,13 @@
         </is>
       </c>
       <c r="D349" s="45" t="n">
-        <v>-4</v>
+        <v>-6</v>
       </c>
       <c r="E349" s="45" t="n">
         <v>-2</v>
       </c>
       <c r="F349" s="43" t="n">
-        <v>-6</v>
+        <v>-8</v>
       </c>
       <c r="G349" s="38" t="n"/>
       <c r="H349" s="38" t="n"/>
@@ -12211,13 +12211,13 @@
         </is>
       </c>
       <c r="D353" s="45" t="n">
-        <v>-4</v>
+        <v>-6</v>
       </c>
       <c r="E353" s="45" t="n">
         <v>-2</v>
       </c>
       <c r="F353" s="43" t="n">
-        <v>-6</v>
+        <v>-8</v>
       </c>
       <c r="G353" s="38" t="n"/>
       <c r="H353" s="38" t="n"/>
@@ -12307,13 +12307,13 @@
         </is>
       </c>
       <c r="D356" s="45" t="n">
-        <v>-6</v>
+        <v>-9</v>
       </c>
       <c r="E356" s="45" t="n">
         <v>-3</v>
       </c>
       <c r="F356" s="43" t="n">
-        <v>-9</v>
+        <v>-12</v>
       </c>
       <c r="G356" s="38" t="n"/>
       <c r="H356" s="38" t="n"/>
@@ -12523,13 +12523,13 @@
         </is>
       </c>
       <c r="D363" s="45" t="n">
-        <v>-4</v>
+        <v>-6</v>
       </c>
       <c r="E363" s="45" t="n">
         <v>-2</v>
       </c>
       <c r="F363" s="43" t="n">
-        <v>-6</v>
+        <v>-8</v>
       </c>
       <c r="G363" s="38" t="n"/>
       <c r="H363" s="38" t="n"/>

--- a/Descuentos/Productos.xlsx
+++ b/Descuentos/Productos.xlsx
@@ -1081,13 +1081,13 @@
         </is>
       </c>
       <c r="D11" s="42" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E11" s="42" t="n">
         <v>-1</v>
       </c>
       <c r="F11" s="43" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="G11" s="38" t="n"/>
       <c r="H11" s="38" t="n"/>
@@ -1305,13 +1305,13 @@
         </is>
       </c>
       <c r="D18" s="42" t="n">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="E18" s="42" t="n">
-        <v>-8</v>
+        <v>-6</v>
       </c>
       <c r="F18" s="43" t="n">
-        <v>244</v>
+        <v>232</v>
       </c>
       <c r="G18" s="38" t="n"/>
       <c r="H18" s="38" t="n"/>
@@ -2337,13 +2337,13 @@
         </is>
       </c>
       <c r="D49" s="42" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E49" s="42" t="n">
         <v>-1</v>
       </c>
       <c r="F49" s="43" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G49" s="38" t="n"/>
       <c r="H49" s="38" t="n"/>
@@ -4157,13 +4157,13 @@
         </is>
       </c>
       <c r="D105" s="42" t="n">
-        <v>0</v>
+        <v>-24</v>
       </c>
       <c r="E105" s="42" t="n">
         <v>-12</v>
       </c>
       <c r="F105" s="43" t="n">
-        <v>-12</v>
+        <v>-36</v>
       </c>
       <c r="G105" s="38" t="n"/>
       <c r="H105" s="38" t="n"/>
@@ -4225,13 +4225,13 @@
         </is>
       </c>
       <c r="D107" s="42" t="n">
-        <v>7</v>
+        <v>-17</v>
       </c>
       <c r="E107" s="42" t="n">
         <v>-12</v>
       </c>
       <c r="F107" s="43" t="n">
-        <v>-5</v>
+        <v>-29</v>
       </c>
       <c r="G107" s="38" t="n"/>
       <c r="H107" s="38" t="n"/>
@@ -4519,13 +4519,13 @@
         </is>
       </c>
       <c r="D116" s="42" t="n">
-        <v>-83</v>
+        <v>-155</v>
       </c>
       <c r="E116" s="42" t="n">
         <v>-36</v>
       </c>
       <c r="F116" s="43" t="n">
-        <v>-119</v>
+        <v>-191</v>
       </c>
       <c r="G116" s="38" t="n"/>
       <c r="H116" s="38" t="n"/>
@@ -6139,13 +6139,13 @@
         </is>
       </c>
       <c r="D166" s="42" t="n">
-        <v>119</v>
+        <v>95</v>
       </c>
       <c r="E166" s="42" t="n">
         <v>-12</v>
       </c>
       <c r="F166" s="43" t="n">
-        <v>107</v>
+        <v>83</v>
       </c>
       <c r="G166" s="38" t="n"/>
       <c r="H166" s="38" t="n"/>
@@ -6567,13 +6567,13 @@
         </is>
       </c>
       <c r="D179" s="42" t="n">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="E179" s="42" t="n">
-        <v>-11</v>
+        <v>-10</v>
       </c>
       <c r="F179" s="43" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="G179" s="38" t="n"/>
       <c r="H179" s="38" t="n"/>
@@ -6839,13 +6839,13 @@
         </is>
       </c>
       <c r="D187" s="42" t="n">
-        <v>1</v>
+        <v>-28</v>
       </c>
       <c r="E187" s="42" t="n">
-        <v>-15</v>
+        <v>-14</v>
       </c>
       <c r="F187" s="43" t="n">
-        <v>-14</v>
+        <v>-42</v>
       </c>
       <c r="G187" s="38" t="n"/>
       <c r="H187" s="38" t="n"/>
@@ -7171,13 +7171,13 @@
         </is>
       </c>
       <c r="D197" s="42" t="n">
-        <v>101</v>
+        <v>80</v>
       </c>
       <c r="E197" s="42" t="n">
-        <v>-11</v>
+        <v>-10</v>
       </c>
       <c r="F197" s="43" t="n">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="G197" s="38" t="n"/>
       <c r="H197" s="38" t="n"/>
@@ -7491,13 +7491,13 @@
         </is>
       </c>
       <c r="D207" s="42" t="n">
-        <v>43</v>
+        <v>3</v>
       </c>
       <c r="E207" s="42" t="n">
         <v>-20</v>
       </c>
       <c r="F207" s="43" t="n">
-        <v>23</v>
+        <v>-17</v>
       </c>
       <c r="G207" s="38" t="n"/>
       <c r="H207" s="38" t="n"/>
@@ -7763,13 +7763,13 @@
         </is>
       </c>
       <c r="D215" s="42" t="n">
-        <v>31</v>
+        <v>-9</v>
       </c>
       <c r="E215" s="42" t="n">
         <v>-20</v>
       </c>
       <c r="F215" s="43" t="n">
-        <v>11</v>
+        <v>-29</v>
       </c>
       <c r="G215" s="38" t="n"/>
       <c r="H215" s="38" t="n"/>
@@ -9343,13 +9343,13 @@
         </is>
       </c>
       <c r="D263" s="42" t="n">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="E263" s="42" t="n">
-        <v>-8</v>
+        <v>-7</v>
       </c>
       <c r="F263" s="43" t="n">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="G263" s="38" t="n"/>
       <c r="H263" s="38" t="n"/>
@@ -9443,13 +9443,13 @@
         </is>
       </c>
       <c r="D266" s="42" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E266" s="42" t="n">
         <v>-1</v>
       </c>
       <c r="F266" s="43" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="G266" s="38" t="n"/>
       <c r="H266" s="38" t="n"/>
@@ -10393,13 +10393,13 @@
         </is>
       </c>
       <c r="D296" s="45" t="n">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="E296" s="45" t="n">
         <v>-2</v>
       </c>
       <c r="F296" s="43" t="n">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="G296" s="38" t="n"/>
       <c r="H296" s="38" t="n"/>
@@ -10439,13 +10439,13 @@
         </is>
       </c>
       <c r="D297" s="45" t="n">
-        <v>894</v>
+        <v>890</v>
       </c>
       <c r="E297" s="45" t="n">
         <v>-2</v>
       </c>
       <c r="F297" s="43" t="n">
-        <v>892</v>
+        <v>888</v>
       </c>
       <c r="G297" s="38" t="n"/>
       <c r="H297" s="38" t="n"/>
@@ -10507,13 +10507,13 @@
         </is>
       </c>
       <c r="D299" s="45" t="n">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="E299" s="45" t="n">
         <v>-2</v>
       </c>
       <c r="F299" s="43" t="n">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="G299" s="38" t="n"/>
       <c r="H299" s="38" t="n"/>
@@ -10923,13 +10923,13 @@
         </is>
       </c>
       <c r="D311" s="45" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="E311" s="45" t="n">
         <v>-2</v>
       </c>
       <c r="F311" s="43" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="G311" s="38" t="n"/>
       <c r="H311" s="38" t="n"/>
@@ -10959,13 +10959,13 @@
         </is>
       </c>
       <c r="D312" s="45" t="n">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="E312" s="45" t="n">
         <v>-2</v>
       </c>
       <c r="F312" s="43" t="n">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="G312" s="38" t="n"/>
       <c r="H312" s="38" t="n"/>
@@ -11713,13 +11713,13 @@
         </is>
       </c>
       <c r="D337" s="45" t="n">
-        <v>-9</v>
+        <v>-15</v>
       </c>
       <c r="E337" s="45" t="n">
         <v>-3</v>
       </c>
       <c r="F337" s="43" t="n">
-        <v>-12</v>
+        <v>-18</v>
       </c>
       <c r="G337" s="38" t="n"/>
       <c r="H337" s="38" t="n"/>
@@ -11989,13 +11989,13 @@
         </is>
       </c>
       <c r="D346" s="45" t="n">
-        <v>-9</v>
+        <v>-15</v>
       </c>
       <c r="E346" s="45" t="n">
         <v>-3</v>
       </c>
       <c r="F346" s="43" t="n">
-        <v>-12</v>
+        <v>-18</v>
       </c>
       <c r="G346" s="38" t="n"/>
       <c r="H346" s="38" t="n"/>
@@ -12085,13 +12085,13 @@
         </is>
       </c>
       <c r="D349" s="45" t="n">
-        <v>-6</v>
+        <v>-10</v>
       </c>
       <c r="E349" s="45" t="n">
         <v>-2</v>
       </c>
       <c r="F349" s="43" t="n">
-        <v>-8</v>
+        <v>-12</v>
       </c>
       <c r="G349" s="38" t="n"/>
       <c r="H349" s="38" t="n"/>
@@ -12211,13 +12211,13 @@
         </is>
       </c>
       <c r="D353" s="45" t="n">
-        <v>-6</v>
+        <v>-10</v>
       </c>
       <c r="E353" s="45" t="n">
         <v>-2</v>
       </c>
       <c r="F353" s="43" t="n">
-        <v>-8</v>
+        <v>-12</v>
       </c>
       <c r="G353" s="38" t="n"/>
       <c r="H353" s="38" t="n"/>
@@ -12307,13 +12307,13 @@
         </is>
       </c>
       <c r="D356" s="45" t="n">
-        <v>-9</v>
+        <v>-15</v>
       </c>
       <c r="E356" s="45" t="n">
         <v>-3</v>
       </c>
       <c r="F356" s="43" t="n">
-        <v>-12</v>
+        <v>-18</v>
       </c>
       <c r="G356" s="38" t="n"/>
       <c r="H356" s="38" t="n"/>
@@ -12523,13 +12523,13 @@
         </is>
       </c>
       <c r="D363" s="45" t="n">
-        <v>-6</v>
+        <v>-10</v>
       </c>
       <c r="E363" s="45" t="n">
         <v>-2</v>
       </c>
       <c r="F363" s="43" t="n">
-        <v>-8</v>
+        <v>-12</v>
       </c>
       <c r="G363" s="38" t="n"/>
       <c r="H363" s="38" t="n"/>

--- a/Descuentos/Productos.xlsx
+++ b/Descuentos/Productos.xlsx
@@ -111,7 +111,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="15">
+  <borders count="17">
     <border>
       <left/>
       <right/>
@@ -279,11 +279,35 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFc6c6c6"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFc6c6c6"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFc6c6c6"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
@@ -420,6 +444,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -824,8 +849,8 @@
         </is>
       </c>
       <c r="D1" s="44" t="n"/>
-      <c r="E1" s="45" t="n"/>
-      <c r="F1" s="1" t="n"/>
+      <c r="E1" s="44" t="n"/>
+      <c r="F1" s="44" t="n"/>
       <c r="G1" s="1" t="n"/>
       <c r="H1" s="1" t="n"/>
       <c r="I1" s="1" t="n"/>
@@ -841,10 +866,7 @@
     <row r="2" ht="18.75" customHeight="1">
       <c r="A2" s="46" t="n"/>
       <c r="B2" s="46" t="n"/>
-      <c r="C2" s="47" t="n"/>
-      <c r="D2" s="48" t="n"/>
-      <c r="E2" s="49" t="n"/>
-      <c r="F2" s="1" t="n"/>
+      <c r="C2" s="50" t="n"/>
       <c r="G2" s="1" t="n"/>
       <c r="H2" s="1" t="n"/>
       <c r="I2" s="1" t="n"/>
@@ -1226,9 +1248,13 @@
           <t>Creatine 150 g UT</t>
         </is>
       </c>
-      <c r="C17" s="20" t="n"/>
+      <c r="C17" s="20" t="n">
+        <v>25</v>
+      </c>
       <c r="D17" s="20" t="n"/>
-      <c r="E17" s="19" t="n"/>
+      <c r="E17" s="19" t="n">
+        <v>25</v>
+      </c>
       <c r="F17" s="1" t="n"/>
       <c r="G17" s="1" t="n"/>
       <c r="H17" s="1" t="n"/>

--- a/Descuentos/Productos.xlsx
+++ b/Descuentos/Productos.xlsx
@@ -1277,9 +1277,13 @@
           <t>Creatine 300 g UT</t>
         </is>
       </c>
-      <c r="C18" s="20" t="n"/>
+      <c r="C18" s="20" t="n">
+        <v>50</v>
+      </c>
       <c r="D18" s="20" t="n"/>
-      <c r="E18" s="19" t="n"/>
+      <c r="E18" s="19" t="n">
+        <v>50</v>
+      </c>
       <c r="F18" s="1" t="n"/>
       <c r="G18" s="1" t="n"/>
       <c r="H18" s="1" t="n"/>

--- a/Descuentos/Productos.xlsx
+++ b/Descuentos/Productos.xlsx
@@ -1223,9 +1223,13 @@
           <t>CREATINA EN COMPRIMIDOS ULTRA TECH</t>
         </is>
       </c>
-      <c r="C16" s="20" t="n"/>
+      <c r="C16" s="20" t="n">
+        <v>-42</v>
+      </c>
       <c r="D16" s="20" t="n"/>
-      <c r="E16" s="19" t="n"/>
+      <c r="E16" s="19" t="n">
+        <v>-42</v>
+      </c>
       <c r="F16" s="1" t="n"/>
       <c r="G16" s="1" t="n"/>
       <c r="H16" s="1" t="n"/>
@@ -1278,11 +1282,11 @@
         </is>
       </c>
       <c r="C18" s="20" t="n">
-        <v>50</v>
+        <v>-91</v>
       </c>
       <c r="D18" s="20" t="n"/>
       <c r="E18" s="19" t="n">
-        <v>50</v>
+        <v>-91</v>
       </c>
       <c r="F18" s="1" t="n"/>
       <c r="G18" s="1" t="n"/>
@@ -3448,9 +3452,13 @@
           <t>Protein Bar x 50 gr chocolate</t>
         </is>
       </c>
-      <c r="C105" s="20" t="n"/>
+      <c r="C105" s="20" t="n">
+        <v>-87</v>
+      </c>
       <c r="D105" s="20" t="n"/>
-      <c r="E105" s="19" t="n"/>
+      <c r="E105" s="19" t="n">
+        <v>-87</v>
+      </c>
       <c r="F105" s="1" t="n"/>
       <c r="G105" s="1" t="n"/>
       <c r="H105" s="1" t="n"/>
@@ -6313,9 +6321,13 @@
           <t>Potasio - Magnesio x 60 caps</t>
         </is>
       </c>
-      <c r="C220" s="20" t="n"/>
+      <c r="C220" s="20" t="n">
+        <v>-71</v>
+      </c>
       <c r="D220" s="20" t="n"/>
-      <c r="E220" s="19" t="n"/>
+      <c r="E220" s="19" t="n">
+        <v>-71</v>
+      </c>
       <c r="F220" s="1" t="n"/>
       <c r="G220" s="1" t="n"/>
       <c r="H220" s="1" t="n"/>
